--- a/data/trans_dic/P55$nadie-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,31</t>
+          <t>0,0; 35,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,58</t>
+          <t>0,0; 33,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,85</t>
+          <t>0,0; 27,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,76</t>
+          <t>0,0; 19,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 24,28</t>
+          <t>2,35; 21,23</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,9</t>
+          <t>0,0; 55,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,35</t>
+          <t>0,0; 26,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,45</t>
+          <t>0,0; 68,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 34,91</t>
+          <t>4,38; 37,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,67</t>
+          <t>0,0; 39,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,45</t>
+          <t>0,0; 26,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 23,0</t>
+          <t>5,3; 22,32</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,71</t>
+          <t>0,0; 32,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 41,91</t>
+          <t>4,12; 41,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,68</t>
+          <t>0,0; 13,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,87</t>
+          <t>0,0; 57,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 58,84</t>
+          <t>6,04; 55,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 29,7</t>
+          <t>3,72; 34,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 27,03</t>
+          <t>2,43; 27,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 32,52</t>
+          <t>2,97; 32,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,46</t>
+          <t>1,17; 10,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,18</t>
+          <t>0,83; 7,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,23</t>
+          <t>0,0; 19,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,37</t>
+          <t>0,0; 20,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 25,0</t>
+          <t>2,8; 23,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 9,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,06</t>
+          <t>1,01; 9,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,04</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,66</t>
+          <t>1,38; 11,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,66</t>
+          <t>1,04; 5,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,15</t>
+          <t>0,0; 11,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,66</t>
+          <t>0,0; 14,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 20,35</t>
+          <t>3,59; 21,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>0,0; 19,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,07</t>
+          <t>0,0; 8,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 20,16</t>
+          <t>2,34; 20,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 9,7</t>
+          <t>3,07; 9,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,31</t>
+          <t>0,0; 14,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,27</t>
+          <t>0,82; 8,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 13,58</t>
+          <t>2,35; 13,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,65</t>
+          <t>3,95; 10,45</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,18</t>
+          <t>3,1; 12,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,1</t>
+          <t>0,08; 5,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,17</t>
+          <t>3,03; 11,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,28</t>
+          <t>1,5; 5,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,8</t>
+          <t>3,04; 12,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,1</t>
+          <t>0,08; 5,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,17</t>
+          <t>3,03; 11,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,3</t>
+          <t>1,51; 5,51</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,48</t>
+          <t>2,15; 10,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,18</t>
+          <t>1,4; 11,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,44</t>
+          <t>3,01; 8,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,35</t>
+          <t>3,71; 10,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,66</t>
+          <t>0,84; 4,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 12,64</t>
+          <t>5,36; 12,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,09</t>
+          <t>3,03; 6,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,5</t>
+          <t>3,77; 8,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,4</t>
+          <t>1,68; 5,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 9,21</t>
+          <t>3,97; 9,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,33</t>
+          <t>3,52; 6,33</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1953</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3996</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4221</t>
+          <t>0; 4524</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3720</t>
+          <t>0; 3821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4880</t>
+          <t>0; 4603</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>652; 6278</t>
+          <t>607; 5490</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7008</t>
+          <t>0; 6034</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1560</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5125</t>
+          <t>0; 4556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1636</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1828</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4594</t>
+          <t>0; 4591</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>584; 4789</t>
+          <t>600; 5088</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6407</t>
+          <t>0; 6456</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2042</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5317</t>
+          <t>0; 4557</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1442; 7170</t>
+          <t>1653; 6959</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5893</t>
+          <t>0; 5785</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1002; 10242</t>
+          <t>1008; 10095</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2899</t>
+          <t>0; 2957</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4648</t>
+          <t>0; 4792</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1898</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>979; 9590</t>
+          <t>985; 9115</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 941</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>897; 7822</t>
+          <t>980; 9103</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1027; 11743</t>
+          <t>1056; 11876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>962; 10660</t>
+          <t>975; 10548</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2336</t>
+          <t>0; 3051</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>839; 7384</t>
+          <t>830; 7341</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5297</t>
+          <t>0; 4914</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1622</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>596; 5174</t>
+          <t>599; 5560</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4504</t>
+          <t>0; 4628</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4869</t>
+          <t>0; 4263</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>959; 8205</t>
+          <t>920; 7816</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3924</t>
+          <t>0; 3873</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>945; 8524</t>
+          <t>948; 9091</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 7125</t>
+          <t>0; 6630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1002; 8474</t>
+          <t>1003; 8179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1230; 7384</t>
+          <t>1154; 6579</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1694</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4018</t>
+          <t>0; 4038</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6464</t>
+          <t>0; 6710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1105; 6118</t>
+          <t>1078; 6377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6852</t>
+          <t>0; 7187</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6743</t>
+          <t>0; 7390</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1325; 10688</t>
+          <t>1243; 10644</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2773; 9040</t>
+          <t>2859; 9131</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6986</t>
+          <t>0; 7356</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>983; 8697</t>
+          <t>982; 9663</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2509; 13623</t>
+          <t>2362; 13587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4850; 13132</t>
+          <t>4874; 12881</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 705</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4429; 17550</t>
+          <t>4459; 17665</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>950; 8731</t>
+          <t>109; 8086</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4237; 16457</t>
+          <t>4468; 17415</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1936; 7451</t>
+          <t>2114; 7786</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4471; 17108</t>
+          <t>4413; 17606</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>950; 8731</t>
+          <t>109; 8086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4237; 16457</t>
+          <t>4468; 17415</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2000; 7585</t>
+          <t>2156; 7889</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2765; 13269</t>
+          <t>2724; 13387</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2039; 14879</t>
+          <t>2040; 16193</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6503</t>
+          <t>0; 6573</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4591; 13072</t>
+          <t>4668; 13450</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8948; 23910</t>
+          <t>8557; 23850</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2212; 12971</t>
+          <t>2349; 13160</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14110; 33385</t>
+          <t>14166; 33609</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9761; 19592</t>
+          <t>9754; 19771</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13766; 33965</t>
+          <t>13473; 31810</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6372; 22919</t>
+          <t>7122; 23224</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15452; 35533</t>
+          <t>15320; 38261</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16390; 30186</t>
+          <t>16765; 30154</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$nadie-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,3</t>
+          <t>0,0; 31,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,85</t>
+          <t>0,0; 35,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,57</t>
+          <t>0,0; 26,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,58</t>
+          <t>0,0; 21,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 21,23</t>
+          <t>2,36; 22,32</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,88</t>
+          <t>0,0; 54,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,1</t>
+          <t>0,0; 27,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,41</t>
+          <t>0,0; 67,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 37,09</t>
+          <t>4,05; 36,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,98</t>
+          <t>0,0; 46,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 31,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 22,32</t>
+          <t>5,18; 22,59</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,11</t>
+          <t>0,0; 32,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 41,31</t>
+          <t>4,05; 43,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,96</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,6</t>
+          <t>0,0; 56,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 55,92</t>
+          <t>5,99; 55,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 34,56</t>
+          <t>3,54; 31,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 27,34</t>
+          <t>2,43; 27,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 32,17</t>
+          <t>2,96; 32,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,39</t>
+          <t>1,18; 10,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,72</t>
+          <t>0,79; 8,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,76</t>
+          <t>0,0; 15,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,46</t>
+          <t>0,0; 25,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 23,81</t>
+          <t>2,95; 26,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,99</t>
+          <t>0,0; 8,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,67</t>
+          <t>1,0; 8,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,25</t>
+          <t>1,33; 10,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,94</t>
+          <t>0,59; 6,5</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1282,64 +1282,64 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,21</t>
+          <t>0,0; 16,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,18</t>
+          <t>0,0; 14,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 21,21</t>
+          <t>3,96; 20,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,74</t>
+          <t>0,0; 19,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,84</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 20,08</t>
+          <t>2,21; 19,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,8</t>
+          <t>2,87; 10,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,01</t>
+          <t>0,0; 15,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,08</t>
+          <t>0,82; 7,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,54</t>
+          <t>2,49; 13,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,45</t>
+          <t>4,11; 10,8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,26</t>
+          <t>2,87; 11,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,65</t>
+          <t>0,65; 5,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,83</t>
+          <t>3,15; 12,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,52</t>
+          <t>1,59; 5,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 12,14</t>
+          <t>3,22; 12,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,65</t>
+          <t>0,65; 5,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,83</t>
+          <t>3,15; 12,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,51</t>
+          <t>1,66; 5,73</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,58</t>
+          <t>2,12; 11,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,08</t>
+          <t>1,36; 10,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,68</t>
+          <t>3,22; 9,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,33</t>
+          <t>3,67; 10,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,72</t>
+          <t>0,78; 4,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 12,72</t>
+          <t>5,42; 12,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,15</t>
+          <t>3,02; 6,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,9</t>
+          <t>3,95; 9,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,47</t>
+          <t>1,46; 5,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,92</t>
+          <t>3,93; 9,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,33</t>
+          <t>3,52; 6,53</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2585</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4235</t>
+          <t>0; 3935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 4752</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3821</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4603</t>
+          <t>0; 4958</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>607; 5490</t>
+          <t>648; 6136</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>4075</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6034</t>
+          <t>0; 5901</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4556</t>
+          <t>0; 5113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>0; 4503</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>600; 5088</t>
+          <t>629; 5604</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6456</t>
+          <t>0; 7551</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4557</t>
+          <t>0; 5563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1653; 6959</t>
+          <t>1777; 7746</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>558</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5785</t>
+          <t>0; 5807</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1008; 10095</t>
+          <t>989; 10583</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2957</t>
+          <t>0; 2568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4792</t>
+          <t>0; 4694</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>985; 9115</t>
+          <t>976; 9032</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,22 +2383,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>980; 9103</t>
+          <t>933; 8379</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1056; 11876</t>
+          <t>1054; 11811</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>975; 10548</t>
+          <t>972; 10497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3051</t>
+          <t>0; 3743</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3437</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>830; 7341</t>
+          <t>836; 7140</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 5260</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2566,47 +2566,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>599; 5560</t>
+          <t>606; 6721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4628</t>
+          <t>0; 3667</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4263</t>
+          <t>0; 5212</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>920; 7816</t>
+          <t>969; 8631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3873</t>
+          <t>0; 3635</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>948; 9091</t>
+          <t>945; 8346</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6630</t>
+          <t>0; 6993</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1003; 8179</t>
+          <t>969; 7956</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1154; 6579</t>
+          <t>700; 7739</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>9111</t>
         </is>
       </c>
     </row>
@@ -2764,64 +2764,64 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4038</t>
+          <t>0; 6076</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6710</t>
+          <t>0; 6805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1078; 6377</t>
+          <t>1301; 6717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7187</t>
+          <t>0; 7017</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7390</t>
+          <t>0; 7616</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1243; 10644</t>
+          <t>1172; 10571</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2859; 9131</t>
+          <t>2894; 10405</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 7356</t>
+          <t>0; 8040</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>982; 9663</t>
+          <t>984; 8809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2362; 13587</t>
+          <t>2497; 14027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4874; 12881</t>
+          <t>5492; 14425</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4923</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4459; 17665</t>
+          <t>4130; 16753</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>109; 8086</t>
+          <t>934; 8362</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4468; 17415</t>
+          <t>4635; 17818</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2114; 7786</t>
+          <t>2417; 8821</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4413; 17606</t>
+          <t>4675; 18267</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>109; 8086</t>
+          <t>934; 8362</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4468; 17415</t>
+          <t>4635; 17818</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2156; 7889</t>
+          <t>2564; 8840</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>24691</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2724; 13387</t>
+          <t>2680; 14318</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2040; 16193</t>
+          <t>1985; 15764</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6573</t>
+          <t>0; 5968</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4668; 13450</t>
+          <t>5351; 15083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8557; 23850</t>
+          <t>8471; 23526</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2349; 13160</t>
+          <t>2183; 12705</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14166; 33609</t>
+          <t>14308; 33361</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9754; 19771</t>
+          <t>10545; 22099</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13473; 31810</t>
+          <t>14130; 32718</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7122; 23224</t>
+          <t>6214; 22767</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15320; 38261</t>
+          <t>15168; 36797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16765; 30154</t>
+          <t>18148; 33629</t>
         </is>
       </c>
     </row>
